--- a/data/trans_dic/P25A$otro-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,53</t>
+          <t>0,86; 7,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 11,92</t>
+          <t>1,78; 12,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 17,49</t>
+          <t>4,51; 17,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 21,31</t>
+          <t>2,64; 21,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,4</t>
+          <t>0,0; 13,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 27,2</t>
+          <t>7,6; 27,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,85</t>
+          <t>1,99; 9,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,94</t>
+          <t>1,87; 10,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 18,29</t>
+          <t>7,15; 18,63</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,52</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,7</t>
+          <t>1,09; 8,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 23,51</t>
+          <t>7,19; 23,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 28,2</t>
+          <t>6,75; 29,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 17,6</t>
+          <t>1,88; 18,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 20,96</t>
+          <t>5,68; 23,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,89</t>
+          <t>2,37; 11,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,83</t>
+          <t>2,13; 9,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 19,14</t>
+          <t>7,9; 19,18</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,45</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 22,94</t>
+          <t>8,34; 22,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 35,68</t>
+          <t>4,6; 38,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,89</t>
+          <t>0,0; 19,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,04</t>
+          <t>0,0; 37,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,18</t>
+          <t>1,62; 8,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,16</t>
+          <t>0,49; 4,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 20,93</t>
+          <t>7,75; 21,1</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,59</t>
+          <t>1,64; 6,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,54</t>
+          <t>0,6; 3,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,63</t>
+          <t>3,49; 9,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 19,98</t>
+          <t>4,47; 20,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 15,35</t>
+          <t>4,34; 15,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 20,5</t>
+          <t>6,22; 20,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,85</t>
+          <t>2,82; 7,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,68</t>
+          <t>2,05; 6,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,48</t>
+          <t>5,02; 11,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 16,52</t>
+          <t>4,23; 16,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 21,64</t>
+          <t>2,6; 22,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 28,68</t>
+          <t>9,84; 28,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,94</t>
+          <t>0,94; 7,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 18,71</t>
+          <t>7,87; 18,24</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,72</t>
+          <t>0,0; 82,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 20,0</t>
+          <t>2,18; 22,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,59</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,04</t>
+          <t>0,0; 19,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 20,54</t>
+          <t>2,03; 19,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,37</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 19,7</t>
+          <t>2,23; 19,32</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,76</t>
+          <t>1,32; 3,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,57</t>
+          <t>1,19; 3,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,09</t>
+          <t>7,13; 11,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,29</t>
+          <t>7,57; 15,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,74</t>
+          <t>3,06; 7,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,13</t>
+          <t>9,37; 17,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,32</t>
+          <t>3,44; 6,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,26</t>
+          <t>2,15; 4,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,9; 13,02</t>
+          <t>8,67; 12,87</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>814; 7215</t>
+          <t>823; 7420</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1909; 13363</t>
+          <t>1996; 14198</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4244; 16323</t>
+          <t>4210; 16067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>987; 8110</t>
+          <t>1006; 8310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6930</t>
+          <t>0; 6797</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4463; 16697</t>
+          <t>4667; 16738</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1969; 11851</t>
+          <t>2666; 12593</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3052; 16276</t>
+          <t>3061; 16945</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10463; 28296</t>
+          <t>11060; 28823</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5208</t>
+          <t>0; 5179</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>965; 8724</t>
+          <t>980; 7990</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4890; 17127</t>
+          <t>5240; 16939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2627; 11412</t>
+          <t>2730; 11992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1095; 9515</t>
+          <t>1018; 9847</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3712; 14031</t>
+          <t>3802; 15684</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3019; 13096</t>
+          <t>2857; 13628</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3050; 14157</t>
+          <t>3065; 14373</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10909; 26759</t>
+          <t>11040; 26810</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5817</t>
+          <t>0; 5908</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4814</t>
+          <t>0; 5296</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7374; 22544</t>
+          <t>8196; 22587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1104; 8697</t>
+          <t>1121; 9464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6643</t>
+          <t>0; 6701</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4357</t>
+          <t>0; 4951</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2081; 12039</t>
+          <t>2130; 11784</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>953; 8197</t>
+          <t>964; 8071</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8212; 23327</t>
+          <t>8641; 23525</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4618; 17920</t>
+          <t>4460; 17469</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026; 11300</t>
+          <t>1902; 10857</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7738; 21921</t>
+          <t>7954; 20589</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2795; 12658</t>
+          <t>2830; 13153</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4101; 17372</t>
+          <t>4916; 17487</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5044; 17770</t>
+          <t>5389; 17460</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9327; 26349</t>
+          <t>9471; 26279</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8891; 24550</t>
+          <t>8851; 26413</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14946; 32963</t>
+          <t>15781; 36270</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1902</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6217</t>
+          <t>0; 6140</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5135; 17790</t>
+          <t>4559; 17894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>935; 7683</t>
+          <t>923; 7970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2014</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6749; 20136</t>
+          <t>6910; 20338</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>927; 7864</t>
+          <t>933; 7879</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 6230</t>
+          <t>0; 6280</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13574; 33288</t>
+          <t>14008; 32455</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1460</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1589</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>0; 4575</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1294; 9800</t>
+          <t>1070; 10857</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5234</t>
+          <t>0; 4894</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5795</t>
+          <t>0; 6989</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1073; 11200</t>
+          <t>1105; 10573</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4937</t>
+          <t>0; 4417</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>929; 8217</t>
+          <t>931; 8058</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8718; 23428</t>
+          <t>8243; 22416</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10634; 29115</t>
+          <t>9690; 27799</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43893; 73216</t>
+          <t>43197; 71994</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18170; 38337</t>
+          <t>18981; 39836</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12083; 29741</t>
+          <t>11755; 29548</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32436; 57294</t>
+          <t>31337; 57940</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29953; 55253</t>
+          <t>30098; 55286</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25737; 51178</t>
+          <t>25772; 50100</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>83701; 122353</t>
+          <t>81461; 120969</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$otro-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,74</t>
+          <t>0,86; 8,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,67</t>
+          <t>1,98; 13,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 17,21</t>
+          <t>4,41; 16,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 21,83</t>
+          <t>2,64; 19,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,15</t>
+          <t>0,0; 12,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 27,26</t>
+          <t>7,53; 29,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,4</t>
+          <t>1,54; 8,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,35</t>
+          <t>1,84; 10,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 18,63</t>
+          <t>6,67; 18,4</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 6,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 8,89</t>
+          <t>1,09; 8,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 23,25</t>
+          <t>7,06; 23,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 29,64</t>
+          <t>5,88; 29,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 18,22</t>
+          <t>1,93; 16,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 23,43</t>
+          <t>5,47; 22,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 11,33</t>
+          <t>2,61; 11,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,98</t>
+          <t>2,1; 9,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 19,18</t>
+          <t>8,08; 19,11</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 22,98</t>
+          <t>7,64; 22,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 38,83</t>
+          <t>4,41; 35,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,05</t>
+          <t>0,0; 19,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,54</t>
+          <t>0,0; 33,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,99</t>
+          <t>1,54; 8,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,09</t>
+          <t>0,35; 4,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 21,1</t>
+          <t>7,78; 21,39</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,42</t>
+          <t>1,65; 6,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,4</t>
+          <t>0,62; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,04</t>
+          <t>3,44; 9,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 20,76</t>
+          <t>4,17; 21,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,45</t>
+          <t>4,18; 15,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 20,14</t>
+          <t>5,85; 19,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,83</t>
+          <t>2,62; 7,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,11</t>
+          <t>1,93; 5,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,54</t>
+          <t>5,14; 11,36</t>
         </is>
       </c>
     </row>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 5,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 16,62</t>
+          <t>4,79; 16,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 22,45</t>
+          <t>2,59; 21,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,29 +1143,29 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 28,97</t>
+          <t>9,33; 28,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,95</t>
+          <t>0,95; 7,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,87; 18,24</t>
+          <t>8,47; 18,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,14</t>
+          <t>0,0; 82,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 22,16</t>
+          <t>2,23; 23,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,03</t>
+          <t>0,0; 9,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,34</t>
+          <t>0,0; 17,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,39</t>
+          <t>2,37; 20,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 19,32</t>
+          <t>2,21; 18,06</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,59</t>
+          <t>1,33; 3,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,41</t>
+          <t>1,1; 3,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,89</t>
+          <t>7,27; 12,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,89</t>
+          <t>7,47; 15,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,69</t>
+          <t>3,18; 7,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,32</t>
+          <t>9,45; 16,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,32</t>
+          <t>3,52; 6,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,17</t>
+          <t>2,16; 4,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,87</t>
+          <t>8,6; 12,71</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>823; 7420</t>
+          <t>825; 7681</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1996; 14198</t>
+          <t>2224; 15559</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4210; 16067</t>
+          <t>4118; 15555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1006; 8310</t>
+          <t>1005; 7496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6797</t>
+          <t>0; 6468</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4667; 16738</t>
+          <t>4622; 18058</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2666; 12593</t>
+          <t>2069; 11256</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3061; 16945</t>
+          <t>3005; 17034</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11060; 28823</t>
+          <t>10318; 28475</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5179</t>
+          <t>0; 5221</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>980; 7990</t>
+          <t>980; 7893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5240; 16939</t>
+          <t>5146; 17326</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2730; 11992</t>
+          <t>2381; 12096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1018; 9847</t>
+          <t>1042; 9098</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3802; 15684</t>
+          <t>3664; 15189</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2857; 13628</t>
+          <t>3145; 14204</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3065; 14373</t>
+          <t>3026; 14027</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11040; 26810</t>
+          <t>11298; 26708</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5908</t>
+          <t>0; 5731</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5296</t>
+          <t>0; 4941</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8196; 22587</t>
+          <t>7514; 22137</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1121; 9464</t>
+          <t>1076; 8648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6701</t>
+          <t>0; 6985</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4951</t>
+          <t>0; 4455</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2130; 11784</t>
+          <t>2021; 11112</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>964; 8071</t>
+          <t>681; 8162</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8641; 23525</t>
+          <t>8667; 23844</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4460; 17469</t>
+          <t>4489; 18287</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1902; 10857</t>
+          <t>1962; 10605</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7954; 20589</t>
+          <t>7845; 22046</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2830; 13153</t>
+          <t>2640; 13560</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4916; 17487</t>
+          <t>4725; 18061</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5389; 17460</t>
+          <t>5066; 16866</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9471; 26279</t>
+          <t>8791; 25684</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8851; 26413</t>
+          <t>8327; 24605</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15781; 36270</t>
+          <t>16147; 35727</t>
         </is>
       </c>
     </row>
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6140</t>
+          <t>0; 7085</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4559; 17894</t>
+          <t>5160; 18284</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>923; 7970</t>
+          <t>919; 7694</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2316,29 +2316,29 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6910; 20338</t>
+          <t>6553; 20126</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>933; 7879</t>
+          <t>939; 7830</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 6280</t>
+          <t>0; 7182</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14008; 32455</t>
+          <t>15065; 32952</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4575</t>
+          <t>0; 4609</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1070; 10857</t>
+          <t>1091; 11291</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4894</t>
+          <t>0; 5667</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6989</t>
+          <t>0; 6252</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1105; 10573</t>
+          <t>1291; 10945</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4417</t>
+          <t>0; 4388</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>931; 8058</t>
+          <t>923; 7532</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8243; 22416</t>
+          <t>8305; 24200</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9690; 27799</t>
+          <t>8965; 27330</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43197; 71994</t>
+          <t>44049; 73170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18981; 39836</t>
+          <t>18728; 38528</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11755; 29548</t>
+          <t>12218; 28767</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31337; 57940</t>
+          <t>31623; 56305</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30098; 55286</t>
+          <t>30772; 55472</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25772; 50100</t>
+          <t>25983; 50135</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>81461; 120969</t>
+          <t>80867; 119456</t>
         </is>
       </c>
     </row>
